--- a/artfynd/A 30257-2026 artfynd.xlsx
+++ b/artfynd/A 30257-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135583261</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135583267</v>
       </c>
       <c r="B3" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135583266</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135583263</v>
       </c>
       <c r="B5" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135583264</v>
       </c>
       <c r="B6" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135583265</v>
       </c>
       <c r="B7" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135583268</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>135583269</v>
       </c>
       <c r="B9" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>135583262</v>
       </c>
       <c r="B10" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30257-2026 artfynd.xlsx
+++ b/artfynd/A 30257-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135583261</v>
       </c>
       <c r="B2" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135583267</v>
       </c>
       <c r="B3" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135583266</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135583263</v>
       </c>
       <c r="B5" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135583264</v>
       </c>
       <c r="B6" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>135583262</v>
       </c>
       <c r="B10" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30257-2026 artfynd.xlsx
+++ b/artfynd/A 30257-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135583261</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135583267</v>
       </c>
       <c r="B3" t="n">
-        <v>81423</v>
+        <v>81425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135583266</v>
       </c>
       <c r="B4" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135583263</v>
       </c>
       <c r="B5" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135583264</v>
       </c>
       <c r="B6" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135583265</v>
       </c>
       <c r="B7" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135583268</v>
       </c>
       <c r="B8" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>135583269</v>
       </c>
       <c r="B9" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>135583262</v>
       </c>
       <c r="B10" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30257-2026 artfynd.xlsx
+++ b/artfynd/A 30257-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135583261</v>
       </c>
       <c r="B2" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135583267</v>
       </c>
       <c r="B3" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135583266</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135583263</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135583264</v>
       </c>
       <c r="B6" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>135583262</v>
       </c>
       <c r="B10" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
